--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/panel_11/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/panel_11/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>16.75604</v>
+      </c>
+      <c r="D2" t="n">
         <v>16.29049</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>16.51481</v>
-      </c>
-      <c r="E2" t="n">
-        <v>16.75604</v>
       </c>
       <c r="F2" t="n">
         <v>42.23984</v>
@@ -611,13 +611,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.2988</v>
+        <v>16.49692</v>
       </c>
       <c r="D8" t="n">
         <v>15.33979</v>
       </c>
       <c r="E8" t="n">
-        <v>16.49692</v>
+        <v>16.2988</v>
       </c>
       <c r="F8" t="n">
         <v>21.01312</v>
